--- a/academias/Lectura, Expresión Oral y Escrita - Estadisticos 20212.xlsx
+++ b/academias/Lectura, Expresión Oral y Escrita - Estadisticos 20212.xlsx
@@ -884,13 +884,13 @@
         <v>15.63</v>
       </c>
       <c r="I12" s="2">
-        <v>9.6</v>
+        <v>8.9</v>
       </c>
       <c r="J12">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>15.63</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1725,13 +1725,13 @@
         <v>15.63</v>
       </c>
       <c r="I12" s="2">
-        <v>9.6</v>
+        <v>8.9</v>
       </c>
       <c r="J12">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>15.63</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/academias/Lectura, Expresión Oral y Escrita - Estadisticos 20212.xlsx
+++ b/academias/Lectura, Expresión Oral y Escrita - Estadisticos 20212.xlsx
@@ -627,25 +627,25 @@
         <v>37</v>
       </c>
       <c r="E5">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F5">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G5" s="1">
-        <v>45.95</v>
+        <v>48.65</v>
       </c>
       <c r="H5" s="1">
-        <v>54.05</v>
+        <v>51.35</v>
       </c>
       <c r="I5" s="2">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J5">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K5" s="1">
-        <v>54.05</v>
+        <v>51.35</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -662,25 +662,25 @@
         <v>41</v>
       </c>
       <c r="E6">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F6">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G6" s="1">
-        <v>29.27</v>
+        <v>34.15</v>
       </c>
       <c r="H6" s="1">
-        <v>70.73</v>
+        <v>65.84999999999999</v>
       </c>
       <c r="I6" s="2">
-        <v>9.699999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="J6">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="K6" s="1">
-        <v>70.73</v>
+        <v>65.84999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -732,25 +732,25 @@
         <v>27</v>
       </c>
       <c r="E8">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8" s="1">
-        <v>96.3</v>
+        <v>100</v>
       </c>
       <c r="H8" s="1">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="I8" s="2">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="J8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>3.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -802,25 +802,25 @@
         <v>44</v>
       </c>
       <c r="E10">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G10" s="1">
-        <v>95.45</v>
+        <v>100</v>
       </c>
       <c r="H10" s="1">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="I10" s="2">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="J10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>4.55</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -991,22 +991,25 @@
         <v>28</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F3">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>53.57</v>
       </c>
       <c r="H3" s="1">
-        <v>100</v>
+        <v>46.43</v>
+      </c>
+      <c r="I3" s="2">
+        <v>6.1</v>
       </c>
       <c r="J3">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1119,22 +1122,25 @@
         <v>44</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="F7">
-        <v>44</v>
+        <v>3</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>93.18000000000001</v>
       </c>
       <c r="H7" s="1">
-        <v>100</v>
+        <v>6.82</v>
+      </c>
+      <c r="I7" s="2">
+        <v>8.699999999999999</v>
       </c>
       <c r="J7">
-        <v>44</v>
+        <v>3</v>
       </c>
       <c r="K7" s="1">
-        <v>100</v>
+        <v>6.82</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1151,22 +1157,25 @@
         <v>27</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F8">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>88.89</v>
       </c>
       <c r="H8" s="1">
-        <v>100</v>
+        <v>11.11</v>
+      </c>
+      <c r="I8" s="2">
+        <v>8.5</v>
       </c>
       <c r="J8">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="K8" s="1">
-        <v>100</v>
+        <v>7.41</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1215,22 +1224,25 @@
         <v>44</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="F10">
-        <v>44</v>
+        <v>5</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>88.64</v>
       </c>
       <c r="H10" s="1">
-        <v>100</v>
+        <v>11.36</v>
+      </c>
+      <c r="I10" s="2">
+        <v>8.1</v>
       </c>
       <c r="J10">
-        <v>44</v>
+        <v>5</v>
       </c>
       <c r="K10" s="1">
-        <v>100</v>
+        <v>11.36</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1247,22 +1259,25 @@
         <v>32</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F11">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>71.88</v>
       </c>
       <c r="H11" s="1">
-        <v>100</v>
+        <v>28.13</v>
+      </c>
+      <c r="I11" s="2">
+        <v>8.5</v>
       </c>
       <c r="J11">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="K11" s="1">
-        <v>100</v>
+        <v>28.13</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1279,22 +1294,25 @@
         <v>32</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F12">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>43.75</v>
       </c>
       <c r="H12" s="1">
-        <v>100</v>
+        <v>56.25</v>
+      </c>
+      <c r="I12" s="2">
+        <v>9.1</v>
       </c>
       <c r="J12">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
+        <v>56.25</v>
       </c>
     </row>
   </sheetData>
@@ -1398,19 +1416,19 @@
         <v>28</v>
       </c>
       <c r="E3">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F3">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="G3" s="1">
-        <v>71.43000000000001</v>
+        <v>53.57</v>
       </c>
       <c r="H3" s="1">
-        <v>28.57</v>
+        <v>46.43</v>
       </c>
       <c r="I3" s="2">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -1468,25 +1486,25 @@
         <v>37</v>
       </c>
       <c r="E5">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F5">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G5" s="1">
-        <v>45.95</v>
+        <v>48.65</v>
       </c>
       <c r="H5" s="1">
-        <v>54.05</v>
+        <v>51.35</v>
       </c>
       <c r="I5" s="2">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J5">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K5" s="1">
-        <v>54.05</v>
+        <v>51.35</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1503,25 +1521,25 @@
         <v>41</v>
       </c>
       <c r="E6">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F6">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G6" s="1">
-        <v>29.27</v>
+        <v>34.15</v>
       </c>
       <c r="H6" s="1">
-        <v>70.73</v>
+        <v>65.84999999999999</v>
       </c>
       <c r="I6" s="2">
-        <v>9.699999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="J6">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="K6" s="1">
-        <v>70.73</v>
+        <v>65.84999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1585,13 +1603,13 @@
         <v>3.7</v>
       </c>
       <c r="I8" s="2">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="J8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>3.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1643,25 +1661,25 @@
         <v>44</v>
       </c>
       <c r="E10">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G10" s="1">
-        <v>95.45</v>
+        <v>100</v>
       </c>
       <c r="H10" s="1">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="I10" s="2">
-        <v>8.699999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="J10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>4.55</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1690,7 +1708,7 @@
         <v>0</v>
       </c>
       <c r="I11" s="2">
-        <v>9.800000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -1725,7 +1743,7 @@
         <v>15.63</v>
       </c>
       <c r="I12" s="2">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J12">
         <v>0</v>

--- a/academias/Lectura, Expresión Oral y Escrita - Estadisticos 20212.xlsx
+++ b/academias/Lectura, Expresión Oral y Escrita - Estadisticos 20212.xlsx
@@ -592,25 +592,25 @@
         <v>36</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F4">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="G4" s="1">
-        <v>11.11</v>
+        <v>38.89</v>
       </c>
       <c r="H4" s="1">
-        <v>88.89</v>
+        <v>61.11</v>
       </c>
       <c r="I4" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J4">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="K4" s="1">
-        <v>88.89</v>
+        <v>52.78</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -627,25 +627,25 @@
         <v>37</v>
       </c>
       <c r="E5">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="F5">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="G5" s="1">
-        <v>48.65</v>
+        <v>75.68000000000001</v>
       </c>
       <c r="H5" s="1">
-        <v>51.35</v>
+        <v>24.32</v>
       </c>
       <c r="I5" s="2">
-        <v>9.300000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J5">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="K5" s="1">
-        <v>51.35</v>
+        <v>24.32</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -662,25 +662,25 @@
         <v>41</v>
       </c>
       <c r="E6">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F6">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="G6" s="1">
-        <v>34.15</v>
+        <v>53.66</v>
       </c>
       <c r="H6" s="1">
-        <v>65.84999999999999</v>
+        <v>46.34</v>
       </c>
       <c r="I6" s="2">
-        <v>9.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J6">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="K6" s="1">
-        <v>65.84999999999999</v>
+        <v>43.9</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -767,25 +767,25 @@
         <v>37</v>
       </c>
       <c r="E9">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G9" s="1">
-        <v>89.19</v>
+        <v>91.89</v>
       </c>
       <c r="H9" s="1">
-        <v>10.81</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="I9" s="2">
-        <v>8.699999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="J9">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K9" s="1">
-        <v>10.81</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1026,22 +1026,25 @@
         <v>36</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F4">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>38.89</v>
       </c>
       <c r="H4" s="1">
-        <v>100</v>
+        <v>61.11</v>
+      </c>
+      <c r="I4" s="2">
+        <v>7.8</v>
       </c>
       <c r="J4">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>52.78</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1058,22 +1061,25 @@
         <v>37</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F5">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>64.86</v>
       </c>
       <c r="H5" s="1">
-        <v>100</v>
+        <v>35.14</v>
+      </c>
+      <c r="I5" s="2">
+        <v>8.300000000000001</v>
       </c>
       <c r="J5">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="K5" s="1">
-        <v>100</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1090,22 +1096,25 @@
         <v>41</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F6">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>41.46</v>
       </c>
       <c r="H6" s="1">
-        <v>100</v>
+        <v>58.54</v>
+      </c>
+      <c r="I6" s="2">
+        <v>8.300000000000001</v>
       </c>
       <c r="J6">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="K6" s="1">
-        <v>100</v>
+        <v>56.1</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1192,22 +1201,25 @@
         <v>37</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F9">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>86.48999999999999</v>
       </c>
       <c r="H9" s="1">
-        <v>100</v>
+        <v>13.51</v>
+      </c>
+      <c r="I9" s="2">
+        <v>8.199999999999999</v>
       </c>
       <c r="J9">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="K9" s="1">
-        <v>100</v>
+        <v>10.81</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1224,25 +1236,25 @@
         <v>44</v>
       </c>
       <c r="E10">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F10">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G10" s="1">
-        <v>88.64</v>
+        <v>93.18000000000001</v>
       </c>
       <c r="H10" s="1">
-        <v>11.36</v>
+        <v>6.82</v>
       </c>
       <c r="I10" s="2">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="J10">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K10" s="1">
-        <v>11.36</v>
+        <v>6.82</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1259,25 +1271,25 @@
         <v>32</v>
       </c>
       <c r="E11">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="F11">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G11" s="1">
-        <v>71.88</v>
+        <v>100</v>
       </c>
       <c r="H11" s="1">
-        <v>28.13</v>
+        <v>0</v>
       </c>
       <c r="I11" s="2">
-        <v>8.5</v>
+        <v>7.8</v>
       </c>
       <c r="J11">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>28.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1294,25 +1306,25 @@
         <v>32</v>
       </c>
       <c r="E12">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="F12">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="G12" s="1">
-        <v>43.75</v>
+        <v>84.38</v>
       </c>
       <c r="H12" s="1">
-        <v>56.25</v>
+        <v>15.63</v>
       </c>
       <c r="I12" s="2">
-        <v>9.1</v>
+        <v>7.4</v>
       </c>
       <c r="J12">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>56.25</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1451,25 +1463,25 @@
         <v>36</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F4">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="G4" s="1">
-        <v>11.11</v>
+        <v>38.89</v>
       </c>
       <c r="H4" s="1">
-        <v>88.89</v>
+        <v>61.11</v>
       </c>
       <c r="I4" s="2">
-        <v>9</v>
+        <v>7.6</v>
       </c>
       <c r="J4">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="K4" s="1">
-        <v>88.89</v>
+        <v>52.78</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1486,25 +1498,25 @@
         <v>37</v>
       </c>
       <c r="E5">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="F5">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="G5" s="1">
-        <v>48.65</v>
+        <v>75.68000000000001</v>
       </c>
       <c r="H5" s="1">
-        <v>51.35</v>
+        <v>24.32</v>
       </c>
       <c r="I5" s="2">
-        <v>9.300000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J5">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="K5" s="1">
-        <v>51.35</v>
+        <v>24.32</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1521,25 +1533,25 @@
         <v>41</v>
       </c>
       <c r="E6">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F6">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="G6" s="1">
-        <v>34.15</v>
+        <v>53.66</v>
       </c>
       <c r="H6" s="1">
-        <v>65.84999999999999</v>
+        <v>46.34</v>
       </c>
       <c r="I6" s="2">
-        <v>9.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J6">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="K6" s="1">
-        <v>65.84999999999999</v>
+        <v>43.9</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1638,13 +1650,13 @@
         <v>10.81</v>
       </c>
       <c r="I9" s="2">
-        <v>8.699999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="J9">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K9" s="1">
-        <v>10.81</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1708,7 +1720,7 @@
         <v>0</v>
       </c>
       <c r="I11" s="2">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -1743,7 +1755,7 @@
         <v>15.63</v>
       </c>
       <c r="I12" s="2">
-        <v>8.800000000000001</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J12">
         <v>0</v>

--- a/academias/Lectura, Expresión Oral y Escrita - Estadisticos 20212.xlsx
+++ b/academias/Lectura, Expresión Oral y Escrita - Estadisticos 20212.xlsx
@@ -662,25 +662,25 @@
         <v>41</v>
       </c>
       <c r="E6">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F6">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G6" s="1">
-        <v>53.66</v>
+        <v>56.1</v>
       </c>
       <c r="H6" s="1">
-        <v>46.34</v>
+        <v>43.9</v>
       </c>
       <c r="I6" s="2">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="J6">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K6" s="1">
-        <v>43.9</v>
+        <v>41.46</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1096,25 +1096,25 @@
         <v>41</v>
       </c>
       <c r="E6">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F6">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G6" s="1">
-        <v>41.46</v>
+        <v>46.34</v>
       </c>
       <c r="H6" s="1">
-        <v>58.54</v>
+        <v>53.66</v>
       </c>
       <c r="I6" s="2">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="J6">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="K6" s="1">
-        <v>56.1</v>
+        <v>51.22</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1533,25 +1533,25 @@
         <v>41</v>
       </c>
       <c r="E6">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F6">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G6" s="1">
-        <v>53.66</v>
+        <v>56.1</v>
       </c>
       <c r="H6" s="1">
-        <v>46.34</v>
+        <v>43.9</v>
       </c>
       <c r="I6" s="2">
         <v>8.699999999999999</v>
       </c>
       <c r="J6">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K6" s="1">
-        <v>43.9</v>
+        <v>41.46</v>
       </c>
     </row>
     <row r="7" spans="1:11">

--- a/academias/Lectura, Expresión Oral y Escrita - Estadisticos 20212.xlsx
+++ b/academias/Lectura, Expresión Oral y Escrita - Estadisticos 20212.xlsx
@@ -959,22 +959,25 @@
         <v>16</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F2">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>81.25</v>
       </c>
       <c r="H2" s="1">
-        <v>100</v>
+        <v>18.75</v>
+      </c>
+      <c r="I2" s="2">
+        <v>8.1</v>
       </c>
       <c r="J2">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="K2" s="1">
-        <v>100</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="3" spans="1:11">

--- a/academias/Lectura, Expresión Oral y Escrita - Estadisticos 20212.xlsx
+++ b/academias/Lectura, Expresión Oral y Escrita - Estadisticos 20212.xlsx
@@ -534,13 +534,13 @@
         <v>12.5</v>
       </c>
       <c r="I2" s="2">
-        <v>8.1</v>
+        <v>7.9</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>6.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -662,25 +662,25 @@
         <v>41</v>
       </c>
       <c r="E6">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F6">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G6" s="1">
-        <v>56.1</v>
+        <v>60.98</v>
       </c>
       <c r="H6" s="1">
-        <v>43.9</v>
+        <v>39.02</v>
       </c>
       <c r="I6" s="2">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="J6">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="K6" s="1">
-        <v>41.46</v>
+        <v>36.59</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -959,25 +959,25 @@
         <v>16</v>
       </c>
       <c r="E2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G2" s="1">
-        <v>81.25</v>
+        <v>87.5</v>
       </c>
       <c r="H2" s="1">
-        <v>18.75</v>
+        <v>12.5</v>
       </c>
       <c r="I2" s="2">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="J2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K2" s="1">
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1064,25 +1064,25 @@
         <v>37</v>
       </c>
       <c r="E5">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F5">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G5" s="1">
-        <v>64.86</v>
+        <v>67.56999999999999</v>
       </c>
       <c r="H5" s="1">
-        <v>35.14</v>
+        <v>32.43</v>
       </c>
       <c r="I5" s="2">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="J5">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K5" s="1">
-        <v>35.14</v>
+        <v>32.43</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1099,25 +1099,25 @@
         <v>41</v>
       </c>
       <c r="E6">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F6">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G6" s="1">
-        <v>46.34</v>
+        <v>56.1</v>
       </c>
       <c r="H6" s="1">
-        <v>53.66</v>
+        <v>43.9</v>
       </c>
       <c r="I6" s="2">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="J6">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="K6" s="1">
-        <v>51.22</v>
+        <v>41.46</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1396,25 +1396,25 @@
         <v>16</v>
       </c>
       <c r="E2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G2" s="1">
-        <v>87.5</v>
+        <v>93.75</v>
       </c>
       <c r="H2" s="1">
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
       <c r="I2" s="2">
-        <v>8.1</v>
+        <v>7.9</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>6.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1431,19 +1431,19 @@
         <v>28</v>
       </c>
       <c r="E3">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F3">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="G3" s="1">
-        <v>53.57</v>
+        <v>75</v>
       </c>
       <c r="H3" s="1">
-        <v>46.43</v>
+        <v>25</v>
       </c>
       <c r="I3" s="2">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -1513,7 +1513,7 @@
         <v>24.32</v>
       </c>
       <c r="I5" s="2">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J5">
         <v>9</v>
@@ -1536,25 +1536,25 @@
         <v>41</v>
       </c>
       <c r="E6">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F6">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G6" s="1">
-        <v>56.1</v>
+        <v>60.98</v>
       </c>
       <c r="H6" s="1">
-        <v>43.9</v>
+        <v>39.02</v>
       </c>
       <c r="I6" s="2">
-        <v>8.699999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J6">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="K6" s="1">
-        <v>41.46</v>
+        <v>36.59</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1723,7 +1723,7 @@
         <v>0</v>
       </c>
       <c r="I11" s="2">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -1746,19 +1746,19 @@
         <v>32</v>
       </c>
       <c r="E12">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F12">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G12" s="1">
-        <v>84.38</v>
+        <v>100</v>
       </c>
       <c r="H12" s="1">
-        <v>15.63</v>
+        <v>0</v>
       </c>
       <c r="I12" s="2">
-        <v>8.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="J12">
         <v>0</v>

--- a/academias/Lectura, Expresión Oral y Escrita - Estadisticos 20212.xlsx
+++ b/academias/Lectura, Expresión Oral y Escrita - Estadisticos 20212.xlsx
@@ -592,25 +592,25 @@
         <v>36</v>
       </c>
       <c r="E4">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F4">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="G4" s="1">
-        <v>38.89</v>
+        <v>63.89</v>
       </c>
       <c r="H4" s="1">
-        <v>61.11</v>
+        <v>36.11</v>
       </c>
       <c r="I4" s="2">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="J4">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>52.78</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -627,25 +627,25 @@
         <v>37</v>
       </c>
       <c r="E5">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F5">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G5" s="1">
-        <v>75.68000000000001</v>
+        <v>83.78</v>
       </c>
       <c r="H5" s="1">
-        <v>24.32</v>
+        <v>16.22</v>
       </c>
       <c r="I5" s="2">
-        <v>8.699999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="J5">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>24.32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -662,25 +662,25 @@
         <v>41</v>
       </c>
       <c r="E6">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F6">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="G6" s="1">
-        <v>60.98</v>
+        <v>73.17</v>
       </c>
       <c r="H6" s="1">
-        <v>39.02</v>
+        <v>26.83</v>
       </c>
       <c r="I6" s="2">
-        <v>8.4</v>
+        <v>7.3</v>
       </c>
       <c r="J6">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>36.59</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -767,25 +767,25 @@
         <v>37</v>
       </c>
       <c r="E9">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G9" s="1">
-        <v>91.89</v>
+        <v>94.59</v>
       </c>
       <c r="H9" s="1">
-        <v>8.109999999999999</v>
+        <v>5.41</v>
       </c>
       <c r="I9" s="2">
         <v>8.4</v>
       </c>
       <c r="J9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>2.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -971,13 +971,13 @@
         <v>12.5</v>
       </c>
       <c r="I2" s="2">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>6.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1029,25 +1029,25 @@
         <v>36</v>
       </c>
       <c r="E4">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F4">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="G4" s="1">
-        <v>38.89</v>
+        <v>63.89</v>
       </c>
       <c r="H4" s="1">
-        <v>61.11</v>
+        <v>36.11</v>
       </c>
       <c r="I4" s="2">
-        <v>7.8</v>
+        <v>6.7</v>
       </c>
       <c r="J4">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>52.78</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1064,25 +1064,25 @@
         <v>37</v>
       </c>
       <c r="E5">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F5">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G5" s="1">
-        <v>67.56999999999999</v>
+        <v>83.78</v>
       </c>
       <c r="H5" s="1">
-        <v>32.43</v>
+        <v>16.22</v>
       </c>
       <c r="I5" s="2">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="J5">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>32.43</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1099,25 +1099,25 @@
         <v>41</v>
       </c>
       <c r="E6">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F6">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G6" s="1">
-        <v>56.1</v>
+        <v>73.17</v>
       </c>
       <c r="H6" s="1">
-        <v>43.9</v>
+        <v>26.83</v>
       </c>
       <c r="I6" s="2">
-        <v>8</v>
+        <v>6.9</v>
       </c>
       <c r="J6">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>41.46</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1134,25 +1134,25 @@
         <v>44</v>
       </c>
       <c r="E7">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G7" s="1">
-        <v>93.18000000000001</v>
+        <v>100</v>
       </c>
       <c r="H7" s="1">
-        <v>6.82</v>
+        <v>0</v>
       </c>
       <c r="I7" s="2">
         <v>8.699999999999999</v>
       </c>
       <c r="J7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>6.82</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1169,25 +1169,25 @@
         <v>27</v>
       </c>
       <c r="E8">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G8" s="1">
-        <v>88.89</v>
+        <v>96.3</v>
       </c>
       <c r="H8" s="1">
-        <v>11.11</v>
+        <v>3.7</v>
       </c>
       <c r="I8" s="2">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="J8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>7.41</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1204,25 +1204,25 @@
         <v>37</v>
       </c>
       <c r="E9">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F9">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G9" s="1">
-        <v>86.48999999999999</v>
+        <v>97.3</v>
       </c>
       <c r="H9" s="1">
-        <v>13.51</v>
+        <v>2.7</v>
       </c>
       <c r="I9" s="2">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="J9">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>10.81</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1239,25 +1239,25 @@
         <v>44</v>
       </c>
       <c r="E10">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F10">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G10" s="1">
-        <v>93.18000000000001</v>
+        <v>100</v>
       </c>
       <c r="H10" s="1">
-        <v>6.82</v>
+        <v>0</v>
       </c>
       <c r="I10" s="2">
         <v>8</v>
       </c>
       <c r="J10">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>6.82</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1466,25 +1466,25 @@
         <v>36</v>
       </c>
       <c r="E4">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F4">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="G4" s="1">
-        <v>38.89</v>
+        <v>63.89</v>
       </c>
       <c r="H4" s="1">
-        <v>61.11</v>
+        <v>36.11</v>
       </c>
       <c r="I4" s="2">
-        <v>7.6</v>
+        <v>6.7</v>
       </c>
       <c r="J4">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>52.78</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1501,25 +1501,25 @@
         <v>37</v>
       </c>
       <c r="E5">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F5">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G5" s="1">
-        <v>75.68000000000001</v>
+        <v>81.08</v>
       </c>
       <c r="H5" s="1">
-        <v>24.32</v>
+        <v>18.92</v>
       </c>
       <c r="I5" s="2">
-        <v>8.699999999999999</v>
+        <v>7.3</v>
       </c>
       <c r="J5">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>24.32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1536,25 +1536,25 @@
         <v>41</v>
       </c>
       <c r="E6">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F6">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G6" s="1">
-        <v>60.98</v>
+        <v>70.73</v>
       </c>
       <c r="H6" s="1">
-        <v>39.02</v>
+        <v>29.27</v>
       </c>
       <c r="I6" s="2">
-        <v>8.300000000000001</v>
+        <v>7</v>
       </c>
       <c r="J6">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>36.59</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1606,19 +1606,19 @@
         <v>27</v>
       </c>
       <c r="E8">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8" s="1">
-        <v>96.3</v>
+        <v>100</v>
       </c>
       <c r="H8" s="1">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="I8" s="2">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -1641,25 +1641,25 @@
         <v>37</v>
       </c>
       <c r="E9">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F9">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G9" s="1">
-        <v>89.19</v>
+        <v>100</v>
       </c>
       <c r="H9" s="1">
-        <v>10.81</v>
+        <v>0</v>
       </c>
       <c r="I9" s="2">
         <v>8.4</v>
       </c>
       <c r="J9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>2.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
